--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487921_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487921_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.1775</v>
+        <v>4.3942</v>
       </c>
       <c r="E2" t="n">
-        <v>6.4812</v>
+        <v>5.9035</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.3038</v>
+        <v>-1.5093</v>
       </c>
       <c r="G2" t="n">
         <v>2.5214</v>
@@ -610,13 +610,13 @@
         <v>1.2487</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0712</v>
+        <v>0.288</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8135</v>
+        <v>0.2358</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2578</v>
+        <v>0.0522</v>
       </c>
       <c r="V2" t="n">
         <v>0.3361</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.983</v>
+        <v>2.1554</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6664</v>
+        <v>2.8388</v>
       </c>
       <c r="F3" t="n">
         <v>-0.6834</v>
@@ -688,10 +688,10 @@
         <v>1.4568</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6491</v>
+        <v>0.8215</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2296</v>
+        <v>0.402</v>
       </c>
       <c r="U3" t="n">
         <v>0.4195</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. JANKOVIC</t>
+          <t>N. DEDOVIC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,40 +721,40 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5861</v>
+        <v>0.4117</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2555</v>
+        <v>-0.0687</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6695</v>
+        <v>0.4804</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.5561</v>
+        <v>0.4963</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.5716</v>
+        <v>-0.5479000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0155</v>
+        <v>1.0442</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2527</v>
+        <v>1.3619</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3513</v>
+        <v>0.3218</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9013</v>
+        <v>1.0401</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.8088</v>
+        <v>-0.8656</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.923</v>
+        <v>-0.8697</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8858</v>
+        <v>0.0041</v>
       </c>
       <c r="P4" t="n">
         <v>-0.2081</v>
@@ -766,19 +766,19 @@
         <v>1.0406</v>
       </c>
       <c r="S4" t="n">
-        <v>2.5366</v>
+        <v>0.1235</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4378</v>
+        <v>-0.1819</v>
       </c>
       <c r="U4" t="n">
-        <v>1.0987</v>
+        <v>0.3054</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8137</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8137</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. DIBBA</t>
+          <t>M. JANKOVIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2122</v>
+        <v>0.2004</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9787</v>
+        <v>1.3983</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7665</v>
+        <v>-1.1979</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1004</v>
+        <v>-1.5561</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6418</v>
+        <v>-1.5716</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7421</v>
+        <v>0.0155</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6434</v>
+        <v>1.2527</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.062</v>
+        <v>0.3513</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7054</v>
+        <v>0.9013</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5431</v>
+        <v>-2.8088</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5798</v>
+        <v>-1.923</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0367</v>
+        <v>-0.8858</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8325</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2081</v>
+        <v>-1.2487</v>
       </c>
       <c r="R5" t="n">
         <v>1.0406</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4469</v>
+        <v>1.1508</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5434</v>
+        <v>0.5806</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0965</v>
+        <v>0.5703</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.1675</v>
+        <v>0.8137</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.8137</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. DEDOVIC</t>
+          <t>L. DIBBA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4471</v>
+        <v>0.044</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6045</v>
+        <v>0.7225</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1574</v>
+        <v>-0.6785</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4963</v>
+        <v>0.1004</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5479000000000001</v>
+        <v>-0.6418</v>
       </c>
       <c r="I6" t="n">
-        <v>1.0442</v>
+        <v>0.7421</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3619</v>
+        <v>0.6434</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3218</v>
+        <v>-0.062</v>
       </c>
       <c r="L6" t="n">
-        <v>1.0401</v>
+        <v>0.7054</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8656</v>
+        <v>-0.5431</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8697</v>
+        <v>-0.5798</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0041</v>
+        <v>0.0367</v>
       </c>
       <c r="P6" t="n">
+        <v>0.8325</v>
+      </c>
+      <c r="Q6" t="n">
         <v>-0.2081</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>-1.2487</v>
       </c>
       <c r="R6" t="n">
         <v>1.0406</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7353</v>
+        <v>0.2787</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7177</v>
+        <v>0.2872</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0176</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4916</v>
+        <v>-0.6891</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4733</v>
+        <v>-0.7295</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0183</v>
+        <v>0.0404</v>
       </c>
       <c r="G7" t="n">
         <v>-0.5679</v>
@@ -1000,13 +1000,13 @@
         <v>0.6244</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4925</v>
+        <v>0.295</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5963000000000001</v>
+        <v>0.3401</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1037</v>
+        <v>-0.045</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. LATORRE SANCHEZ</t>
+          <t>S. CECILIA PEREZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8607</v>
+        <v>-0.7781</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7156</v>
+        <v>1.17</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.5764</v>
+        <v>-1.9481</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.5263</v>
+        <v>-1.369</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.1132</v>
+        <v>-2.3879</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4131</v>
+        <v>1.0189</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1259</v>
+        <v>1.2152</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2435</v>
+        <v>-0.6568000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1176</v>
+        <v>1.872</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.4004</v>
+        <v>-2.5842</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8697</v>
+        <v>-1.7311</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5306999999999999</v>
+        <v>-0.8532</v>
       </c>
       <c r="P8" t="n">
-        <v>1.2487</v>
+        <v>0.8325</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2487</v>
+        <v>0.8325</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3981</v>
+        <v>-0.2416</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8416</v>
+        <v>-0.0452</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5565</v>
+        <v>-0.1964</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.9813</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.9813</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. CECILIA PEREZ</t>
+          <t>A. LATORRE SANCHEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1942</v>
+        <v>-1.2703</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7833</v>
+        <v>0.3942</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.9775</v>
+        <v>-1.6644</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.369</v>
+        <v>-1.5263</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.3879</v>
+        <v>-1.1132</v>
       </c>
       <c r="I9" t="n">
-        <v>1.0189</v>
+        <v>-0.4131</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2152</v>
+        <v>-0.1259</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6568000000000001</v>
+        <v>-0.2435</v>
       </c>
       <c r="L9" t="n">
-        <v>1.872</v>
+        <v>0.1176</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.5842</v>
+        <v>-1.4004</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.7311</v>
+        <v>-0.8697</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8532</v>
+        <v>-0.5306999999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8325</v>
+        <v>1.2487</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8325</v>
+        <v>1.2487</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6576</v>
+        <v>0.9886</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4319</v>
+        <v>0.5201</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2257</v>
+        <v>0.4685</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.9813</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.9813</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2058</v>
+        <v>-1.601</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6536</v>
+        <v>-2.225</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4477</v>
+        <v>0.6239</v>
       </c>
       <c r="G10" t="n">
         <v>-0.5278</v>
@@ -1234,13 +1234,13 @@
         <v>0.8325</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4293</v>
+        <v>0.1755</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.261</v>
+        <v>0.1677</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1683</v>
+        <v>0.0078</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6936</v>
+        <v>-1.8261</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5415</v>
+        <v>-0.7914</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1521</v>
+        <v>-1.0347</v>
       </c>
       <c r="G11" t="n">
         <v>-1.2991</v>
@@ -1312,13 +1312,13 @@
         <v>1.4568</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6889</v>
+        <v>0.1786</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8358</v>
+        <v>-0.0857</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1468</v>
+        <v>0.2643</v>
       </c>
       <c r="V11" t="n">
         <v>1.1675</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.5835</v>
+        <v>-5.2327</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.2547</v>
+        <v>-1.9333</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.3288</v>
+        <v>-3.2994</v>
       </c>
       <c r="G12" t="n">
         <v>-5.6772</v>
@@ -1390,13 +1390,13 @@
         <v>0.6244</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4495</v>
+        <v>-0.0987</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4319</v>
+        <v>-0.1105</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0176</v>
+        <v>0.0118</v>
       </c>
       <c r="V12" t="n">
         <v>1.1675</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.5177</v>
+        <v>-4.191600000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>6.353100000000001</v>
+        <v>6.6794</v>
       </c>
       <c r="F13" t="n">
-        <v>-10.8712</v>
+        <v>-10.871</v>
       </c>
       <c r="G13" t="n">
         <v>-9.655200000000001</v>
@@ -1468,10 +1468,10 @@
         <v>11.4466</v>
       </c>
       <c r="S13" t="n">
-        <v>3.633799999999999</v>
+        <v>3.9599</v>
       </c>
       <c r="T13" t="n">
-        <v>1.7839</v>
+        <v>2.1102</v>
       </c>
       <c r="U13" t="n">
         <v>1.8499</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.8277</v>
+        <v>5.7476</v>
       </c>
       <c r="E14" t="n">
-        <v>4.4915</v>
+        <v>4.9201</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3362</v>
+        <v>0.8275</v>
       </c>
       <c r="G14" t="n">
         <v>2.7624</v>
@@ -1546,13 +1546,13 @@
         <v>0.8325</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.1241</v>
+        <v>-0.2042</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.1586</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5369</v>
+        <v>-0.0456</v>
       </c>
       <c r="V14" t="n">
         <v>2.565</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.3322</v>
+        <v>3.0885</v>
       </c>
       <c r="E15" t="n">
-        <v>3.5301</v>
+        <v>2.8871</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1979</v>
+        <v>0.2014</v>
       </c>
       <c r="G15" t="n">
         <v>2.61</v>
@@ -1624,13 +1624,13 @@
         <v>0.6244</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8658</v>
+        <v>0.6221</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8416</v>
+        <v>0.1986</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0242</v>
+        <v>0.4235</v>
       </c>
       <c r="V15" t="n">
         <v>1.5213</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.6692</v>
+        <v>3.0557</v>
       </c>
       <c r="E16" t="n">
-        <v>5.9178</v>
+        <v>6.1321</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.2486</v>
+        <v>-3.0764</v>
       </c>
       <c r="G16" t="n">
         <v>5.1901</v>
@@ -1702,13 +1702,13 @@
         <v>0.6244</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4991</v>
+        <v>-0.1125</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5219</v>
+        <v>-0.3076</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0229</v>
+        <v>0.1951</v>
       </c>
       <c r="V16" t="n">
         <v>-1.3975</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. CEBOLLA HERRERA</t>
+          <t>T. SAGNA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.0783</v>
+        <v>2.2258</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6735</v>
+        <v>2.2397</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4048</v>
+        <v>-0.0139</v>
       </c>
       <c r="G17" t="n">
-        <v>2.2232</v>
+        <v>1.0966</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7846</v>
+        <v>2.5033</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4385</v>
+        <v>-1.4067</v>
       </c>
       <c r="J17" t="n">
-        <v>2.7826</v>
+        <v>2.7663</v>
       </c>
       <c r="K17" t="n">
-        <v>1.7033</v>
+        <v>2.6096</v>
       </c>
       <c r="L17" t="n">
-        <v>1.0793</v>
+        <v>0.1568</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5595</v>
+        <v>-1.6697</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9187</v>
+        <v>-0.1063</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3592</v>
+        <v>-1.5634</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6244</v>
+        <v>1.4568</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6649</v>
+        <v>1.4568</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7692</v>
+        <v>-0.3277</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.5266999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7007</v>
+        <v>0.199</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. SAGNA</t>
+          <t>J. CEBOLLA HERRERA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.644</v>
+        <v>2.0989</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9182</v>
+        <v>1.4592</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2742</v>
+        <v>0.6397</v>
       </c>
       <c r="G18" t="n">
-        <v>1.0966</v>
+        <v>2.2232</v>
       </c>
       <c r="H18" t="n">
-        <v>2.5033</v>
+        <v>0.7846</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.4067</v>
+        <v>1.4385</v>
       </c>
       <c r="J18" t="n">
-        <v>2.7663</v>
+        <v>2.7826</v>
       </c>
       <c r="K18" t="n">
-        <v>2.6096</v>
+        <v>1.7033</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1568</v>
+        <v>1.0793</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.6697</v>
+        <v>-0.5595</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1063</v>
+        <v>-0.9187</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.5634</v>
+        <v>0.3592</v>
       </c>
       <c r="P18" t="n">
-        <v>1.4568</v>
+        <v>0.6244</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4568</v>
+        <v>1.6649</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9094</v>
+        <v>-0.7486</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8482</v>
+        <v>-0.2829</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0613</v>
+        <v>-0.4658</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7443</v>
+        <v>-0.7062</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7289</v>
+        <v>-0.9432</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0154</v>
+        <v>0.237</v>
       </c>
       <c r="G19" t="n">
         <v>-0.4771</v>
@@ -1936,13 +1936,13 @@
         <v>0.6244</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1064</v>
+        <v>0.1445</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3229</v>
+        <v>0.1086</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2165</v>
+        <v>0.0359</v>
       </c>
       <c r="V19" t="n">
         <v>1.2914</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. OLAIZOLA GARIN</t>
+          <t>I. MIRANDA GARCIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0114</v>
+        <v>-1.2544</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8591</v>
+        <v>-1.6693</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1523</v>
+        <v>0.415</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.3178</v>
+        <v>0.7138</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1942</v>
+        <v>-0.5884</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.512</v>
+        <v>1.3022</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3338</v>
+        <v>0.6528</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3985</v>
+        <v>-0.0044</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.7323</v>
+        <v>0.6572</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.984</v>
+        <v>0.061</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2043</v>
+        <v>-0.5839</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7796999999999999</v>
+        <v>0.645</v>
       </c>
       <c r="P20" t="n">
-        <v>0.8325</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8731</v>
+        <v>1.6649</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2253</v>
+        <v>-0.3844</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5153</v>
+        <v>-0.2409</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7099</v>
+        <v>-0.1435</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.7513</v>
+        <v>-1.1675</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.7513</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. MIRANDA GARCIA</t>
+          <t>M. OLAIZOLA GARIN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.294</v>
+        <v>-1.943</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.5622</v>
+        <v>-1.2877</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2682</v>
+        <v>-0.6553</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7138</v>
+        <v>-1.3178</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5884</v>
+        <v>0.1942</v>
       </c>
       <c r="I21" t="n">
-        <v>1.3022</v>
+        <v>-1.512</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6528</v>
+        <v>-0.3338</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.0044</v>
+        <v>0.3985</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6572</v>
+        <v>-0.7323</v>
       </c>
       <c r="M21" t="n">
-        <v>0.061</v>
+        <v>-0.984</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5839</v>
+        <v>-0.2043</v>
       </c>
       <c r="O21" t="n">
-        <v>0.645</v>
+        <v>-0.7796999999999999</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.4162</v>
+        <v>0.8325</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6649</v>
+        <v>1.8731</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4241</v>
+        <v>0.2936</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1338</v>
+        <v>0.0867</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2903</v>
+        <v>0.2069</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.1675</v>
+        <v>-1.7513</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.1675</v>
+        <v>-1.7513</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9332</v>
+        <v>-2.5403</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7227</v>
+        <v>-0.6156</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.2105</v>
+        <v>-1.9247</v>
       </c>
       <c r="G22" t="n">
         <v>-1.0294</v>
@@ -2170,13 +2170,13 @@
         <v>0.4162</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7144</v>
+        <v>-0.3215</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3915</v>
+        <v>-0.2843</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3229</v>
+        <v>-0.0372</v>
       </c>
       <c r="V22" t="n">
         <v>-1.3975</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0508</v>
+        <v>-3.1118</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.7872</v>
+        <v>-2.2514</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.2636</v>
+        <v>-0.8604000000000001</v>
       </c>
       <c r="G23" t="n">
         <v>-2.1167</v>
@@ -2248,13 +2248,13 @@
         <v>1.6649</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3909</v>
+        <v>-0.452</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9786</v>
+        <v>-0.4429</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4123</v>
+        <v>-0.0091</v>
       </c>
       <c r="V23" t="n">
         <v>-1.1675</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>4.517700000000002</v>
+        <v>6.660799999999998</v>
       </c>
       <c r="E24" t="n">
         <v>10.871</v>
       </c>
       <c r="F24" t="n">
-        <v>-6.353300000000001</v>
+        <v>-4.2101</v>
       </c>
       <c r="G24" t="n">
         <v>9.655099999999997</v>
@@ -2305,19 +2305,19 @@
         <v>14.2082</v>
       </c>
       <c r="L24" t="n">
-        <v>4.245499999999999</v>
+        <v>4.2455</v>
       </c>
       <c r="M24" t="n">
-        <v>-8.798299999999999</v>
+        <v>-8.798300000000001</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.8179999999999998</v>
+        <v>-0.8179999999999999</v>
       </c>
       <c r="O24" t="n">
         <v>-7.9803</v>
       </c>
       <c r="P24" t="n">
-        <v>0.000199999999999867</v>
+        <v>0.0001999999999996449</v>
       </c>
       <c r="Q24" t="n">
         <v>-11.4465</v>
@@ -2326,13 +2326,13 @@
         <v>11.4465</v>
       </c>
       <c r="S24" t="n">
-        <v>-3.6337</v>
+        <v>-1.4907</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.8499</v>
+        <v>-1.85</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.7839</v>
+        <v>0.3592</v>
       </c>
       <c r="V24" t="n">
         <v>-1.5036</v>
